--- a/frontend/test-reports/e2e-test-report.xlsx
+++ b/frontend/test-reports/e2e-test-report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/23/2026, 9:36:09 AM</t>
+    <t>7/23/2026, 9:42:53 AM</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>6.01 seconds</t>
+    <t>2.17 seconds</t>
   </si>
   <si>
     <t>#</t>
@@ -80,7 +80,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:07.844Z</t>
+    <t>2026-07-23T04:12:52.137Z</t>
   </si>
   <si>
     <t/>
@@ -89,43 +89,43 @@
     <t>2. Role Selection Page - Should display User and Organization roles</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:07.966Z</t>
+    <t>2026-07-23T04:12:52.300Z</t>
   </si>
   <si>
     <t>3. User Login Page - Should contain required login inputs</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:08.144Z</t>
+    <t>2026-07-23T04:12:52.503Z</t>
   </si>
   <si>
     <t>4. Organization Login Page - Should contain required login inputs</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:08.309Z</t>
+    <t>2026-07-23T04:12:52.665Z</t>
   </si>
   <si>
     <t>5. User Signup Page - Should render form inputs properly</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:08.468Z</t>
+    <t>2026-07-23T04:12:52.814Z</t>
   </si>
   <si>
     <t>6. Organization Signup Page - Should render form inputs properly</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:08.592Z</t>
+    <t>2026-07-23T04:12:52.964Z</t>
   </si>
   <si>
     <t>7. User Dashboard Page - Should load navigation and sections</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:09.174Z</t>
+    <t>2026-07-23T04:12:53.269Z</t>
   </si>
   <si>
     <t>8. Crowd Monitor Page - Should render monitoring container</t>
   </si>
   <si>
-    <t>2026-07-23T04:06:09.329Z</t>
+    <t>2026-07-23T04:12:53.433Z</t>
   </si>
 </sst>
 </file>
@@ -717,7 +717,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="11">
-        <v>4526</v>
+        <v>877</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>22</v>
@@ -740,7 +740,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="11">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>25</v>
@@ -763,7 +763,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="11">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>27</v>
@@ -786,7 +786,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="11">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>29</v>
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="11">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>31</v>
@@ -832,7 +832,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="11">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>33</v>
@@ -855,7 +855,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="11">
-        <v>581</v>
+        <v>304</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
@@ -878,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="11">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>37</v>

--- a/frontend/test-reports/e2e-test-report.xlsx
+++ b/frontend/test-reports/e2e-test-report.xlsx
@@ -26,7 +26,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/23/2026, 9:42:53 AM</t>
+    <t>7/23/2026, 9:46:13 AM</t>
   </si>
   <si>
     <t>Total Test Cases</t>
@@ -47,7 +47,7 @@
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>2.17 seconds</t>
+    <t>2.87 seconds</t>
   </si>
   <si>
     <t>#</t>
@@ -80,7 +80,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:52.137Z</t>
+    <t>2026-07-23T04:16:11.864Z</t>
   </si>
   <si>
     <t/>
@@ -89,43 +89,43 @@
     <t>2. Role Selection Page - Should display User and Organization roles</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:52.300Z</t>
+    <t>2026-07-23T04:16:12.048Z</t>
   </si>
   <si>
     <t>3. User Login Page - Should contain required login inputs</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:52.503Z</t>
+    <t>2026-07-23T04:16:12.305Z</t>
   </si>
   <si>
     <t>4. Organization Login Page - Should contain required login inputs</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:52.665Z</t>
+    <t>2026-07-23T04:16:12.493Z</t>
   </si>
   <si>
     <t>5. User Signup Page - Should render form inputs properly</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:52.814Z</t>
+    <t>2026-07-23T04:16:12.756Z</t>
   </si>
   <si>
     <t>6. Organization Signup Page - Should render form inputs properly</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:52.964Z</t>
+    <t>2026-07-23T04:16:12.901Z</t>
   </si>
   <si>
     <t>7. User Dashboard Page - Should load navigation and sections</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:53.269Z</t>
+    <t>2026-07-23T04:16:13.255Z</t>
   </si>
   <si>
     <t>8. Crowd Monitor Page - Should render monitoring container</t>
   </si>
   <si>
-    <t>2026-07-23T04:12:53.433Z</t>
+    <t>2026-07-23T04:16:13.448Z</t>
   </si>
 </sst>
 </file>
@@ -717,7 +717,7 @@
         <v>21</v>
       </c>
       <c r="E2" s="11">
-        <v>877</v>
+        <v>1292</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>22</v>
@@ -740,7 +740,7 @@
         <v>21</v>
       </c>
       <c r="E3" s="11">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>25</v>
@@ -763,7 +763,7 @@
         <v>21</v>
       </c>
       <c r="E4" s="11">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>27</v>
@@ -786,7 +786,7 @@
         <v>21</v>
       </c>
       <c r="E5" s="11">
-        <v>160</v>
+        <v>188</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>29</v>
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="E6" s="11">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>31</v>
@@ -832,7 +832,7 @@
         <v>21</v>
       </c>
       <c r="E7" s="11">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>33</v>
@@ -855,7 +855,7 @@
         <v>21</v>
       </c>
       <c r="E8" s="11">
-        <v>304</v>
+        <v>353</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>35</v>
@@ -878,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="E9" s="11">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>37</v>
